--- a/premise/data/additional_inventories/lci-lithium.xlsx
+++ b/premise/data/additional_inventories/lci-lithium.xlsx
@@ -12521,8 +12521,12 @@
       <c r="A6" t="s">
         <v>81</v>
       </c>
-      <c r="B6" t="s">
-        <v>138</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>APPROVED LITHIUM-HYDROXIDE QUICKLIME IDENTITY, issue85, 2026-10-18. Kelly,Wang,Dai,Winjobi2021 DOI10.1016/j.resconrec.2021.105762 Table3 Material and energy flow summary per tonneLiOH.H2O:1.05tonneLi2CO3,1.15tonneCaO,0.5m3water,5000MJelectricity,3000MJdiesel,21000MJnaturalgas. https://www.osti.gov/servlets/purl/1868964 . Replace1.15kg precipitatedCaCO3 purchase with1.15kg quicklime,milled,packed,RoW per1kg battery-gradeLiOH.H2O output. SourceCaO reagent was mistranscribed asCaCO3 product. The existing output name lithiumhydroxide,batterygrade is kept for compatibility but chemically means MONOHYDRATE,not anhydrousLiOH; downstream hydration-equivalent corrections remain valid. Preserve source1.05kgLi2CO3 split across five brines,and all operating-energy/water/emission quantities. This is a direct source transcription correction,not a fabricated closed reaction:CaCO3 is a causticization residue,not the incominglime. SourceTable3 does not specify full residue/slurry composition,excessCaO hydration,process-water circulation,Li recovery or treatment. Do not invent a CaCO3 sales credit,100%process yield or additional arbitrarysolidwaste.0.5kgwaterconsumed is sourceconsumptivewater,not a completegrossreaction-waterbalance. No change to hydroxide/carbonate marketshares,shipping,elemental-Li factors,native suppliers or primary-secondaryshares.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Source: Jarod C. Kelly, Michael Wang, Qiang Dai, Olumide Winjobi, Energy, greenhouse gas, and water life cycle analysis of lithium carbonate and lithium hydroxide monohydrate from brine and ore resources and their use in lithium ion battery cathodes and lithium ion batteries, Resources, Conservation and Recycling, Volume 174, 2021, 105762, ISSN 0921-3449, https://doi.org/10.1016/j.resconrec.2021.105762.</t>
+        </is>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
@@ -12715,14 +12719,20 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>141</v>
-      </c>
-      <c r="B15" t="s">
-        <v>142</v>
-      </c>
-      <c r="C15" t="s">
-        <v>37</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>market for quicklime, milled, packed</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>quicklime, milled, packed</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
       </c>
       <c r="D15">
         <v>1.1499999999999999</v>
